--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008545626218323586</v>
       </c>
       <c r="C2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>52078630</v>
+        <v>3927255</v>
       </c>
       <c r="L2" t="n">
-        <v>26938543</v>
+        <v>1640355</v>
       </c>
       <c r="M2" t="n">
-        <v>6228375</v>
+        <v>298868</v>
       </c>
       <c r="N2" t="n">
-        <v>257308</v>
+        <v>4163</v>
       </c>
       <c r="O2" t="n">
-        <v>3666340</v>
+        <v>164510</v>
       </c>
       <c r="P2" t="n">
-        <v>1294955</v>
+        <v>178</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999741911888123</v>
+        <v>0.9999387264251709</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8225782513618469</v>
+        <v>0.7068057060241699</v>
       </c>
       <c r="S2" t="n">
-        <v>0.688319206237793</v>
+        <v>0.5126057863235474</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6065511107444763</v>
+        <v>0.3722198903560638</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2690760493278503</v>
+        <v>0.04639887809753418</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6594300270080566</v>
+        <v>0.39222651720047</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8090035319328308</v>
+        <v>0.229974165558815</v>
       </c>
       <c r="X2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558068513870239</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117310047149658</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579899072647095</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614375710487366</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019421935081482</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002047782815014169</v>
       </c>
       <c r="C3" t="n">
-        <v>313</v>
+        <v>105</v>
       </c>
       <c r="D3" t="n">
-        <v>52078630</v>
+        <v>3927255</v>
       </c>
       <c r="E3" t="n">
-        <v>8035136</v>
+        <v>993746</v>
       </c>
       <c r="F3" t="n">
-        <v>256600</v>
+        <v>44665</v>
       </c>
       <c r="G3" t="n">
-        <v>16763</v>
+        <v>2527</v>
       </c>
       <c r="H3" t="n">
-        <v>18828</v>
+        <v>4237</v>
       </c>
       <c r="I3" t="n">
-        <v>941</v>
+        <v>99</v>
       </c>
       <c r="J3" t="n">
-        <v>120833473</v>
+        <v>10069231</v>
       </c>
       <c r="K3" t="n">
-        <v>125351960</v>
+        <v>9814278</v>
       </c>
       <c r="L3" t="n">
-        <v>145147164</v>
+        <v>11502870</v>
       </c>
       <c r="M3" t="n">
-        <v>181695884</v>
+        <v>14965809</v>
       </c>
       <c r="N3" t="n">
-        <v>195217352</v>
+        <v>16240205</v>
       </c>
       <c r="O3" t="n">
-        <v>188971197</v>
+        <v>15647962</v>
       </c>
       <c r="P3" t="n">
-        <v>194363681</v>
+        <v>16221354</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8621260523796082</v>
+        <v>0.7897735834121704</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6794652938842773</v>
+        <v>0.4891540110111237</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5533390641212463</v>
+        <v>0.315886378288269</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2392025291919708</v>
+        <v>0.0461345799267292</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5983632802963257</v>
+        <v>0.3206060230731964</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5575466156005859</v>
+        <v>0.0009172893478535116</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2382014</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102565</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82163</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120835440</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>133910484</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>153853413</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184139493</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>195552500</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190264326</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>194510227</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957497239112854</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097340106964111</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569492101669312</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.660748302936554</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012896418571472</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03221459809678776</v>
       </c>
       <c r="C4" t="n">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>10284284</v>
+        <v>1440167</v>
       </c>
       <c r="E4" t="n">
-        <v>26938543</v>
+        <v>1640355</v>
       </c>
       <c r="F4" t="n">
-        <v>2071668</v>
+        <v>224681</v>
       </c>
       <c r="G4" t="n">
-        <v>94183</v>
+        <v>13186</v>
       </c>
       <c r="H4" t="n">
-        <v>241074</v>
+        <v>34938</v>
       </c>
       <c r="I4" t="n">
-        <v>16829</v>
+        <v>103</v>
       </c>
       <c r="J4" t="n">
-        <v>1967</v>
+        <v>389</v>
       </c>
       <c r="K4" t="n">
-        <v>11232829</v>
+        <v>1629088</v>
       </c>
       <c r="L4" t="n">
-        <v>12198157</v>
+        <v>1559677</v>
       </c>
       <c r="M4" t="n">
-        <v>4040133</v>
+        <v>504066</v>
       </c>
       <c r="N4" t="n">
-        <v>698957</v>
+        <v>85559</v>
       </c>
       <c r="O4" t="n">
-        <v>1893522</v>
+        <v>254916</v>
       </c>
       <c r="P4" t="n">
-        <v>305724</v>
+        <v>596</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999870657920837</v>
+        <v>0.9999693632125854</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8418880105018616</v>
+        <v>0.7459897994995117</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6838635802268982</v>
+        <v>0.5006054043769836</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5787245035171509</v>
+        <v>0.3417471647262573</v>
       </c>
       <c r="U4" t="n">
-        <v>0.253261387348175</v>
+        <v>0.0462663546204567</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6274142265319824</v>
+        <v>0.3528182804584503</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6601399779319763</v>
+        <v>0.001827290281653404</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2497781</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>999552</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>66772</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13821</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2674305</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3491908</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1596524</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>363809</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600393</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566512703895569</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107314348220825</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574692010879517</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610927581787109</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016157984733582</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>682369</v>
+        <v>139201</v>
       </c>
       <c r="E5" t="n">
-        <v>3291245</v>
+        <v>404873</v>
       </c>
       <c r="F5" t="n">
-        <v>6228375</v>
+        <v>298868</v>
       </c>
       <c r="G5" t="n">
-        <v>211048</v>
+        <v>21760</v>
       </c>
       <c r="H5" t="n">
-        <v>777103</v>
+        <v>81215</v>
       </c>
       <c r="I5" t="n">
-        <v>65638</v>
+        <v>160</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8328581</v>
+        <v>1045379</v>
       </c>
       <c r="L5" t="n">
-        <v>12708136</v>
+        <v>1713098</v>
       </c>
       <c r="M5" t="n">
-        <v>5027608</v>
+        <v>647257</v>
       </c>
       <c r="N5" t="n">
-        <v>818383</v>
+        <v>86073</v>
       </c>
       <c r="O5" t="n">
-        <v>2460941</v>
+        <v>348612</v>
       </c>
       <c r="P5" t="n">
-        <v>1027640</v>
+        <v>193872</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999899864196777</v>
+        <v>0.9999762773513794</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9006994962692261</v>
+        <v>0.8370816707611084</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8735669851303101</v>
+        <v>0.800635039806366</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9539690017700195</v>
+        <v>0.9298657774925232</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9922974705696106</v>
+        <v>0.9895448088645935</v>
       </c>
       <c r="V5" t="n">
-        <v>0.977895200252533</v>
+        <v>0.9632353782653809</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9932313561439514</v>
+        <v>0.9881537556648254</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97322</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1034594</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>119997</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>350660</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2567472</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3578747</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1610177</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>364930</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604826</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733909368515015</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641069173812866</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837216734886169</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963006377220154</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.99388188123703</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983799457550049</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>322</v>
+        <v>54</v>
       </c>
       <c r="D6" t="n">
-        <v>184807</v>
+        <v>24119</v>
       </c>
       <c r="E6" t="n">
-        <v>245292</v>
+        <v>29277</v>
       </c>
       <c r="F6" t="n">
-        <v>274511</v>
+        <v>24318</v>
       </c>
       <c r="G6" t="n">
-        <v>257308</v>
+        <v>4163</v>
       </c>
       <c r="H6" t="n">
-        <v>103825</v>
+        <v>8238</v>
       </c>
       <c r="I6" t="n">
-        <v>9626</v>
+        <v>67</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78611</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64601</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>131879</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84061</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>275</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>75955</v>
+        <v>23296</v>
       </c>
       <c r="E7" t="n">
-        <v>564806</v>
+        <v>115534</v>
       </c>
       <c r="F7" t="n">
-        <v>1283339</v>
+        <v>172603</v>
       </c>
       <c r="G7" t="n">
-        <v>323876</v>
+        <v>36947</v>
       </c>
       <c r="H7" t="n">
-        <v>3666340</v>
+        <v>164510</v>
       </c>
       <c r="I7" t="n">
-        <v>212690</v>
+        <v>167</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9726</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358547</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91683</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>754</v>
+        <v>94</v>
       </c>
       <c r="D8" t="n">
-        <v>5414</v>
+        <v>2305</v>
       </c>
       <c r="E8" t="n">
-        <v>61678</v>
+        <v>16247</v>
       </c>
       <c r="F8" t="n">
-        <v>154015</v>
+        <v>37799</v>
       </c>
       <c r="G8" t="n">
-        <v>53087</v>
+        <v>11139</v>
       </c>
       <c r="H8" t="n">
-        <v>752692</v>
+        <v>126288</v>
       </c>
       <c r="I8" t="n">
-        <v>1294955</v>
+        <v>178</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
